--- a/data/trans_orig/IP21B-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP21B-Estudios-trans_orig.xlsx
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>63,7%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>1877</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>631</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5431</t>
+          <t>5633</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>714</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6081</t>
+          <t>6204</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2445</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9030</t>
+          <t>9340</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>22,52%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11544</t>
+          <t>11342</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16345</t>
+          <t>16344</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18422</t>
+          <t>18299</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23829</t>
+          <t>23789</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>32449</t>
+          <t>32139</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>39034</t>
+          <t>38913</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>93,81%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>583</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5737</t>
+          <t>5282</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1462</t>
+          <t>1877</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8152</t>
+          <t>7536</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3318</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11486</t>
+          <t>11013</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>18,81%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19674</t>
+          <t>20129</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24730</t>
+          <t>24828</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25002</t>
+          <t>25618</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31692</t>
+          <t>31277</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>47079</t>
+          <t>47552</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>55247</t>
+          <t>55249</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,34%</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2462</t>
+          <t>2561</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3010</t>
+          <t>2982</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>56,29%</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>621</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2287</t>
+          <t>2315</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6695</t>
+          <t>7386</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1203</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6666</t>
+          <t>6583</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3344</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11274</t>
+          <t>11187</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,08%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14838</t>
+          <t>14147</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20230</t>
+          <t>20203</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14695</t>
+          <t>14778</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>20146</t>
+          <t>20158</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>31621</t>
+          <t>31708</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>39545</t>
+          <t>39551</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,2%</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3224</t>
+          <t>3202</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>611</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4654</t>
+          <t>4365</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>55,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>679</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6311</t>
+          <t>6408</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>52,04%</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>1175</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>3569</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7350</t>
+          <t>7323</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>11633</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>94,49%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1669</t>
+          <t>1559</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8673</t>
+          <t>8175</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3001</t>
+          <t>2687</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9808</t>
+          <t>9777</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5781</t>
+          <t>5821</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15126</t>
+          <t>15389</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,44%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19353</t>
+          <t>19851</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26357</t>
+          <t>26467</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22669</t>
+          <t>22700</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29476</t>
+          <t>29790</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>45377</t>
+          <t>45114</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>54722</t>
+          <t>54682</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,38%</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4158</t>
+          <t>3984</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>748</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5919</t>
+          <t>5998</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1547</t>
+          <t>1604</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7881</t>
+          <t>8323</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>31,06%</t>
         </is>
       </c>
     </row>
@@ -4395,7 +4395,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7973</t>
+          <t>8147</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8747</t>
+          <t>8668</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13931</t>
+          <t>13918</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>18916</t>
+          <t>18474</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25250</t>
+          <t>25193</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,02%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>722</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4963</t>
+          <t>5150</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2331</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6225</t>
+          <t>6047</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>49,0%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2237</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6062</t>
+          <t>6478</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2809</t>
+          <t>2248</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>43,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6115</t>
+          <t>6293</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11066</t>
+          <t>11100</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,95%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2078</t>
+          <t>2157</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8339</t>
+          <t>8692</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>1597</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8486</t>
+          <t>8186</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5348</t>
+          <t>5266</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14049</t>
+          <t>14230</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,94%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12889</t>
+          <t>12536</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19150</t>
+          <t>19071</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12211</t>
+          <t>12511</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18753</t>
+          <t>19100</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>27876</t>
+          <t>27695</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>36577</t>
+          <t>36659</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,44%</t>
         </is>
       </c>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3670</t>
+          <t>3433</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>643</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4947</t>
+          <t>4956</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>63,77%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>884</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6267</t>
+          <t>6547</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>49,53%</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1792</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2810</t>
+          <t>2801</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>7114</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6952</t>
+          <t>6672</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12384</t>
+          <t>12335</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,31%</t>
         </is>
       </c>
     </row>
@@ -6233,7 +6233,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3151</t>
+          <t>3051</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2590</t>
+          <t>2175</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>654</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4635</t>
+          <t>4721</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>74,43%</t>
         </is>
       </c>
     </row>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>702</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>415</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1708</t>
+          <t>1622</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5733</t>
+          <t>5689</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>89,69%</t>
         </is>
       </c>
     </row>
@@ -6576,7 +6576,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4824</t>
+          <t>4782</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>908</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6519</t>
+          <t>6874</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2647</t>
+          <t>2390</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9845</t>
+          <t>9907</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,71%</t>
         </is>
       </c>
     </row>
@@ -6684,7 +6684,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4391</t>
+          <t>4433</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -6699,7 +6699,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5942</t>
+          <t>5587</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11696</t>
+          <t>11553</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11830</t>
+          <t>11768</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19028</t>
+          <t>19285</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>88,97%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP21B-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP21B-Estudios-trans_orig.xlsx
@@ -538,13 +538,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si estuvo en lista de espera en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si, en los últimos 12 meses, estuvieron en lista de espera para ingresar, al menos una noche, en un hospital en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,107 +723,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1336</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3352</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>39,86%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1336</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2710</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>39,86%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3359</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>25,84%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>80,85%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1336</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3293</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>25,84%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>64,98%</t>
         </is>
       </c>
     </row>
@@ -841,69 +841,69 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3352</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>60,14%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>1818</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>3352</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>60,14%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>19,15%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>6</t>
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1877</t>
+          <t>1811</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3352</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3352</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3352</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>1818</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>1818</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>1818</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>3352</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>3352</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>3352</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1071,67 +1071,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>2733</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6113</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>11,15%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,79%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>24,95%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>2469</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>631</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5633</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>639</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5635</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>14,55%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,72%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>33,18%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2733</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>714</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6204</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>11,15%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2566</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9340</t>
+          <t>9298</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,42%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>21770</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>18390</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>23820</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>88,85%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>75,05%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,21%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>14506</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>11342</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>16344</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>11340</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>16336</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>85,45%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>66,82%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,28%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>21770</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>18299</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>23789</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>88,85%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>32139</t>
+          <t>32181</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>38913</t>
+          <t>38998</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>94,02%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>24503</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>24503</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>24503</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>16975</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>16975</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>16975</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>24503</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>24503</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>24503</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1522,47 +1522,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5298</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>6618</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>5298</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5298</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5298</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>5298</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>6618</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>6618</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>6618</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>5298</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>5298</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>5298</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4069</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1421</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7603</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>12,27%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4,29%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>22,93%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2469</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>583</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5282</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5511</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>9,72%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,29%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>20,79%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>4069</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1877</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7536</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>12,27%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3316</t>
+          <t>3148</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11013</t>
+          <t>11170</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,07%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>29085</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>25551</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>31733</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>87,73%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>77,07%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>95,71%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>22942</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>20129</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>24828</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>19900</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>24773</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>90,28%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>79,21%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,71%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>29085</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>25618</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>31277</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>87,73%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>47552</t>
+          <t>47395</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>55249</t>
+          <t>55417</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,62%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>33154</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>33154</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>33154</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>25411</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>25411</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>25411</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>33154</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>33154</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>33154</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2141,13 +2141,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si estuvo en lista de espera en 2012 (tasa de respuesta: 97,75%)</t>
+          <t>Menores según si, en los últimos 12 meses, estuvieron en lista de espera para ingresar, al menos una noche, en un hospital en 2012 (tasa de respuesta: 97,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,107 +2326,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>21,11%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>80,72%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>672</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2561</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>21,11%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>2694</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>12,68%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>80,49%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>672</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2982</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>12,68%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>50,86%</t>
         </is>
       </c>
     </row>
@@ -2439,74 +2439,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2510</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3182</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>78,89%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>19,28%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>2115</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>2510</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>621</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>3182</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>78,89%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>19,51%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>7</t>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2315</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3182</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3182</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3182</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>2115</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>2115</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>2115</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>3182</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>3182</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>3182</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2674,67 +2674,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>3187</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1204</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7122</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>14,92%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,64%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>33,34%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>3430</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1330</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7386</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1351</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6613</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>15,93%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6,18%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>34,3%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3187</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1203</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6583</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>14,92%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3344</t>
+          <t>3404</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11187</t>
+          <t>11336</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,43%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>18174</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>14239</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>20157</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>85,08%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>66,66%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,36%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>18103</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>14147</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>14920</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>20182</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>84,07%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>65,7%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>93,82%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>18174</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>14778</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>20158</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>85,08%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>31708</t>
+          <t>31559</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>39551</t>
+          <t>39491</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,06%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>21361</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>21361</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>21361</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>21533</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>21533</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>21533</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>21361</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>21361</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>21361</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4384</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>25,16%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7,18%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>55,26%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3202</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3163</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>21,09%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>73,16%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>611</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4365</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>25,16%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>7,7%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>712</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6408</t>
+          <t>6344</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>51,53%</t>
         </is>
       </c>
     </row>
@@ -3125,74 +3125,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5938</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3550</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>7364</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>74,84%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>44,74%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>92,82%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>3454</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1175</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>1214</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>4377</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>78,91%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>26,84%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>27,73%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>5938</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>3569</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>7323</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>74,84%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>44,98%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>92,3%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>13</t>
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>5968</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11633</t>
+          <t>11600</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,22%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7934</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7934</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>7934</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>4377</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>4377</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>4377</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>7934</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>7934</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>7934</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5854</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2630</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10136</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>18,03%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8,1%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>31,21%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>4353</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1559</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8175</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1463</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>8427</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>15,53%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>5,56%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>29,17%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>5854</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2687</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>9777</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>18,03%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5821</t>
+          <t>5902</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15389</t>
+          <t>15280</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,26%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>26623</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>22341</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>29847</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>81,97%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>68,79%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>91,9%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>23673</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>19851</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>26467</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>19599</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>26563</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>84,47%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>70,83%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>94,44%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>26623</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>22700</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>29790</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>81,97%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>45114</t>
+          <t>45223</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>54682</t>
+          <t>54601</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,25%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>32477</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>32477</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>32477</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>28026</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>28026</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>28026</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>32477</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>32477</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>32477</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3744,13 +3744,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si estuvo en lista de espera en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si, en los últimos 12 meses, estuvieron en lista de espera para ingresar, al menos una noche, en un hospital en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3934,67 +3934,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>676</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>1897</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>35,63%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>891</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>1221</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>1897</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>64,37%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>1897</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>1897</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>1897</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>891</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>891</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>891</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2954</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6225</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>20,14%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,18%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>42,45%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1363</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3984</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4218</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>11,24%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>32,84%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2954</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>748</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5998</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>20,14%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>5,1%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1604</t>
+          <t>1958</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8323</t>
+          <t>8196</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,58%</t>
         </is>
       </c>
     </row>
@@ -4385,74 +4385,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11712</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8441</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>13907</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>79,86%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>57,55%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,82%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>10768</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>8147</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>7913</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>12131</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>88,76%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>67,16%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>65,23%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>11712</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>8668</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>13918</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>79,86%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>59,1%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>94,9%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>33</t>
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>18474</t>
+          <t>18601</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25193</t>
+          <t>24839</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>92,69%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>14666</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>14666</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>14666</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>12131</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>12131</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>12131</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>14666</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>14666</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>14666</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2382</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>10,67%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>46,35%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>2738</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>722</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5150</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>729</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5277</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>38,03%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10,03%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>71,52%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>549</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2892</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>10,67%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>1236</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6047</t>
+          <t>6172</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>50,02%</t>
         </is>
       </c>
     </row>
@@ -4733,67 +4733,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>4591</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2758</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5140</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>89,33%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>53,65%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>4462</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2050</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>6478</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>1923</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>6471</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>61,97%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>28,48%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>89,97%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>4591</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>2248</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>5140</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>89,33%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6293</t>
+          <t>6168</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11100</t>
+          <t>11104</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,98%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5140</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5140</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>5140</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>7200</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>7200</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>7200</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>5140</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>5140</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>5140</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4394</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1642</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8458</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>21,23%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7,93%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>40,87%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>4777</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2157</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8692</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2089</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>8479</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>22,51%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>10,16%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>40,95%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>4394</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1597</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>8186</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>21,23%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5266</t>
+          <t>5116</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14230</t>
+          <t>14107</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>33,65%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>12239</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>19055</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>78,77%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>59,13%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>92,07%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>16451</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>12536</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>19071</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>12749</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>19139</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>77,49%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>59,05%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>89,84%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>16303</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>12511</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>19100</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>78,77%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>27695</t>
+          <t>27818</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>36659</t>
+          <t>36809</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,8%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>20697</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>20697</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>20697</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>21228</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>21228</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>21228</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>20697</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>20697</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>20697</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5347,13 +5347,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si estuvo en lista de espera en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si, en los últimos 12 meses, estuvieron en lista de espera para ingresar, al menos una noche, en un hospital en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5537,57 +5537,57 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -5645,82 +5645,82 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>2113</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -5758,92 +5758,92 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2113</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2113</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>2113</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2256</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>535</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4802</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>32,35%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7,67%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>68,85%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>822</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3433</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>15,05%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3366</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>16,61%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>62,85%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2275</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>643</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4956</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>29,33%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>8,29%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>3098</t>
+          <t>3116</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>968</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6547</t>
+          <t>6344</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>52,22%</t>
         </is>
       </c>
     </row>
@@ -5988,74 +5988,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4718</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2172</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6439</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>67,65%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>31,15%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>92,33%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>4640</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5462</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>84,95%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>37,15%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>4317</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1810</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5177</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>83,39%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>34,96%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>5482</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>2801</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>7114</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>70,67%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>36,11%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>91,71%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>17</t>
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>10121</t>
+          <t>9034</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6672</t>
+          <t>5806</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12335</t>
+          <t>11182</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>92,03%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>6974</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>6974</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>6974</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>5462</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>5462</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>5462</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7757</t>
+          <t>5177</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7757</t>
+          <t>5177</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7757</t>
+          <t>5177</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>13219</t>
+          <t>12150</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>13219</t>
+          <t>12150</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13219</t>
+          <t>12150</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>743</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1905</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>32,4%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>83,1%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1421</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1497</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3051</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>37,85%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3121</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>40,91%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>81,29%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2175</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>35,72%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2346</t>
+          <t>2240</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>623</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4721</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>72,29%</t>
         </is>
       </c>
     </row>
@@ -6331,74 +6331,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1549</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>387</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2292</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>67,6%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>16,9%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>2332</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>702</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>3753</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>62,15%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>18,71%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>2162</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3659</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>59,09%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>14,7%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>1665</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>415</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>2590</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>64,28%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>16,03%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>7</t>
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>3997</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1622</t>
+          <t>1649</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5689</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>63,02%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,53%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2292</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2292</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2292</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>3753</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>3753</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3753</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2590</t>
+          <t>3659</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2590</t>
+          <t>3659</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2590</t>
+          <t>3659</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>6343</t>
+          <t>5951</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6343</t>
+          <t>5951</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6343</t>
+          <t>5951</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2999</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>877</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6332</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>26,48%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7,75%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>55,91%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>2243</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4782</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>24,34%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6,65%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>51,89%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>666</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6874</t>
+          <t>4896</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>55,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>5443</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2390</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9907</t>
+          <t>9061</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>44,95%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>8326</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4993</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>10448</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>73,52%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>44,09%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>92,25%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>6972</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>4433</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>8602</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>75,66%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>48,11%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>93,35%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>9260</t>
+          <t>6478</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>3939</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11553</t>
+          <t>8169</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>16232</t>
+          <t>14804</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11768</t>
+          <t>11099</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19285</t>
+          <t>17816</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>88,37%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>11325</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>11325</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>11325</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>9215</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>9215</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>9215</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12461</t>
+          <t>8835</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12461</t>
+          <t>8835</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12461</t>
+          <t>8835</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>21675</t>
+          <t>20160</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>21675</t>
+          <t>20160</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>21675</t>
+          <t>20160</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
